--- a/data_extactor/batch_10_fa/trimmed/batch_0055_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0055_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | ایمنی و امنیت عمومی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | جغرافیا | مدیریت و امور اداری</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زیست‌شناسی | خدمات مشتری و شخصی | جغرافیا | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ماموران کنترل حیوانات | دانشمندان حفاظت محیط زیست | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | کارشناسان بازرسی و پیشگیری از آتش‌سوزی جنگل‌ها | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>ماموران کنترل و ساماندهی حیوانات | دانشمندان حفاظت از منابع طبیعی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | حقوق و مقررات دولتی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | قانون و دولت | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | مرتب‌سازی اطلاعات | درک شفاهی | دید نزدیک | دید دور | توجه انتخابی</t>
+          <t>بیان شفاهی | وضوح گفتار | ترتیب‌دهی اطلاعات | درک شفاهی | بینایی نزدیک | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارشناسان انطباق با قوانین و مقررات | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | سرپرستان رده‌اول کارکنان حراست و انتظامات | پارکبانان | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | تکنسین‌های ترافیک و عبور و مرور</t>
+          <t>کارشناسان پایش انطباق و بازرسی مقرراتی | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | سرپرستان رده‌اول کارکنان حراست و انتظامات | متصدیان پارکینگ | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | تکنسین‌های ترافیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | روان‌شناسی | خدمات مشتریان و خدمات فردی | مخابرات | ترابری و حمل‌ونقل</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | روان‌شناسی | خدمات مشتری و شخصی | مخابرات | حمل و نقل</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ماموران زندان و ندامتگاه | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان کشف جرم | سرپرستان رده‌اول پلیس و کارآگاهان | کارشناسان تشخیص هویت و سوابق کیفری پلیس | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
+          <t>مأموران زندان و بازداشتگاه | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول پلیس و کارآگاهان | کارشناسان تشخیص هویت و ثبت سوابق پلیس | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | جغرافیا | زبان خارجی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | جغرافیا | زبان خارجی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | دید نزدیک | درک کتبی | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | درک کتبی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازرسان محصولات کشاورزی | کارگزاران گمرکی و ترخیص‌کاران | کارآگاهان و بازرسان کشف جرم | کارشناسان و تحلیل‌گران بررسی تخلفات مالی | تحلیل‌گران اطلاعاتی و امنیتی | ماموران گشت پلیس و کلانتری | ماموران بازرسی و غربالگری امنیت حمل‌ونقل</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | حق‌العمل‌کاران و کارگزاران گمرکی | کارآگاهان و بازرسان جنایی | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران داده‌ها و اطلاعات امنیتی | ماموران گشت پلیس و کلانتری | ماموران بازرسی و کنترل امنیتی حمل‌ونقل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | ترابری و حمل‌ونقل | جغرافیا | مخابرات</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | خدمات مشتری و شخصی | حمل و نقل | جغرافیا | مخابرات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | دید نزدیک | دید دور</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ماموران زندان و ندامتگاه | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان کشف جرم | سرپرستان رده‌اول پلیس و کارآگاهان | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | ماموران بازرسی و غربالگری امنیت حمل‌ونقل</t>
+          <t>مأموران زندان و بازداشتگاه | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول پلیس و کارآگاهان | ماموران گشت پلیس و کلانتری | نگهبانان و ماموران حراست | ماموران بازرسی و کنترل امنیتی حمل‌ونقل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | زیست‌شناسی | ترابری و حمل‌ونقل</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | خدمات مشتری و شخصی | آموزش و پرورش | زیست‌شناسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متصدیان مراقبت و نگهداری حیوانات | مربیان آموزش حیوانات | کارگران دامپروری، پرورش آبزیان و امور دام | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | ماموران گشت پلیس و کلانتری | دامپزشکان | دستیاران دامپزشکی و متصدیان حیوانات آزمایشگاهی</t>
+          <t>مراقبان و نگهداران حیوانات | مربیان و رام‌کنندگان حیوانات | کارگران پرورش دام، طیور و آبزیان | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | ماموران گشت پلیس و کلانتری | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | رایانه و الکترونیک | امور اداری و دفتری | ایمنی و امنیت عمومی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | اداری | ایمنی و امنیت عمومی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان ارزیابی، رسیدگی و خسارت بیمه | کارآگاهان و بازرسان کشف جرم | کارشناسان و تحلیل‌گران بررسی تخلفات مالی | تحلیل‌گران اطلاعاتی و امنیتی | کارشناسان تشخیص هویت و سوابق کیفری پلیس | ماموران گشت پلیس و کلانتری | کارشناسان حفاظت و پیشگیری از خسارت فروشگاهی</t>
+          <t>کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارآگاهان و بازرسان جنایی | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | ماموران گشت پلیس و کلانتری | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | امور اداری و دفتری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | اداری | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | دید دور | درک شفاهی | دید نزدیک | استدلال استقرایی | استدلال قیاسی</t>
+          <t>حساسیت به مسئله | توجه انتخابی | بینایی دور | درک شفاهی | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارآگاهان و بازرسان کشف جرم | سرپرستان رده‌اول کارکنان خدمات سرگرمی و بازی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان و تحلیل‌گران بررسی تخلفات مالی | کارآگاهان و بازرسان خصوصی | کارشناسان حفاظت و پیشگیری از خسارت فروشگاهی | متخصصان مدیریت امنیت و حراست</t>
+          <t>کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان بازرسی، کشف و تحلیل تقلب | کارآگاهان و بازرسان خصوصی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | مخابرات | حقوق و مقررات دولتی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | مخابرات | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید دور | درک شفاهی | تشخیص گفتار | دید نزدیک | توجه انتخابی | بیان شفاهی</t>
+          <t>حساسیت به مسئله | بینایی دور | درک شفاهی | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ماموران زندان و ندامتگاه | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | کارشناسان حفاظت و پیشگیری از خسارت فروشگاهی | ماموران بازرسی و غربالگری امنیت حمل‌ونقل</t>
+          <t>مأموران زندان و بازداشتگاه | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | ماموران بازرسی و کنترل امنیتی حمل‌ونقل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | دید دور | توجه انتخابی | تشخیص گفتار</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | بینایی دور | توجه انتخابی | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس‌های شهری و بین‌شهری | کارگران نگهداری و راهداری بزرگراه‌ها | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | ناظران و همراهان اتوبوس مدرسه | نگهبانان و ماموران حراست | تکنسین‌های ترافیک و عبور و مرور</t>
+          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | کارگران راهداری و نگهداری جاده‌ها | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | مراقبین و متصدیان سرویس مدارس | نگهبانان و ماموران حراست | تکنسین‌های ترافیک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
